--- a/Result/profitability/8932.xlsx
+++ b/Result/profitability/8932.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.27</v>
       </c>
       <c r="M2" t="n">
-        <v>0.60125</v>
+        <v>0.6499999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>56.1825</v>
+        <v>57.54125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.12</v>
       </c>
       <c r="M3" t="n">
-        <v>0.59</v>
+        <v>0.55375</v>
       </c>
       <c r="N3" t="n">
-        <v>52.12</v>
+        <v>50.4925</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.24</v>
       </c>
       <c r="M4" t="n">
-        <v>0.50875</v>
+        <v>0.4712499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>44.9025</v>
+        <v>45.47499999999999</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.04</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4012499999999999</v>
+        <v>0.35625</v>
       </c>
       <c r="N5" t="n">
-        <v>39.18</v>
+        <v>38.68625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.28</v>
       </c>
       <c r="M6" t="n">
-        <v>0.24625</v>
+        <v>0.17375</v>
       </c>
       <c r="N6" t="n">
-        <v>31.39</v>
+        <v>30.68625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.59</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1725</v>
+        <v>0.19625</v>
       </c>
       <c r="N7" t="n">
-        <v>25.66</v>
+        <v>25.26</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1276,7 +1276,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.08</v>
       </c>
       <c r="M8" t="n">
-        <v>0.13125</v>
+        <v>0.14</v>
       </c>
       <c r="N8" t="n">
-        <v>19.05</v>
+        <v>18.995</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>-0.08</v>
       </c>
       <c r="M9" t="n">
-        <v>0.05499999999999999</v>
+        <v>0.05499999999999998</v>
       </c>
       <c r="N9" t="n">
         <v>13.00125</v>
@@ -1645,7 +1645,7 @@
         <v>0.05</v>
       </c>
       <c r="M10" t="n">
-        <v>0.095</v>
+        <v>0.09499999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>13.07875</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8932</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>686</v>
+      </c>
+      <c r="D75" t="n">
+        <v>269</v>
+      </c>
+      <c r="E75" t="n">
+        <v>417</v>
+      </c>
+      <c r="F75" t="n">
+        <v>60.75</v>
+      </c>
+      <c r="G75" t="n">
+        <v>302</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>44.08%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>9</v>
+      </c>
+      <c r="J75" t="n">
+        <v>311</v>
+      </c>
+      <c r="K75" t="n">
+        <v>212</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="N75" t="n">
+        <v>62.09875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.06999999999999995</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1320754716981132</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.4399999999999977</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.00719071743748978</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.375</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.950000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.06105100463678526</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
